--- a/data/trending_integrated_20261027_11.xlsx
+++ b/data/trending_integrated_20261027_11.xlsx
@@ -578,10 +578,10 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
         <v>66</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41458154930</v>
+        <v>41590652030</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18695587925</v>
+        <v>18699108465</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>나무가, 휴머노이드 로봇 '아틀라스' 공급망 확정. 3D 센싱 기술 보유.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 뉴스가 주가 급등의 주요 요인으로 작용. LG이노텍을 제치고 공급사로 채택되었다는 점이 부각되며 텐버거 기대감이 형성됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['휴머노이드', '아틀라스', '3D센싱']</t>
+          <t>['아틀라스', '휴머노이드', '공급망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -747,215 +747,215 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1360000</v>
+        <v>20600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.67%</t>
+          <t>'+8.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>469</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>1556</v>
+        <v>114</v>
       </c>
       <c r="H4" t="n">
-        <v>48.66</v>
+        <v>0.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1275000</v>
+        <v>19050</v>
       </c>
       <c r="K4" t="n">
-        <v>1346000</v>
+        <v>19450</v>
       </c>
       <c r="L4" t="n">
-        <v>1381000</v>
+        <v>22450</v>
       </c>
       <c r="M4" t="n">
-        <v>1345000</v>
+        <v>18430</v>
       </c>
       <c r="N4" t="n">
-        <v>48.69</v>
+        <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>1880200906500</v>
+        <v>58313523265</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>62100</v>
       </c>
       <c r="Q4" t="n">
-        <v>501000</v>
+        <v>14600</v>
       </c>
       <c r="R4" t="n">
-        <v>174000</v>
+        <v>7000</v>
       </c>
       <c r="S4" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4조 규모 자사주 소각 및 주주환원 발표 기대감, 외국인/기관의 쌍끌이 매수를 근거로 15% 이상 상승 전망. 긍정적인 체결 강도 확인.</t>
+          <t>브릴스, 로봇 기업으로 빅웨이브 기대감. 기술 특례 상장 기업.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['자사주', '주주환원', '외국인', '기관']</t>
+          <t>['로봇', '빅웨이브', '기술특례']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20200</v>
+        <v>1361000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.04%</t>
+          <t>'+6.75%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>471</v>
       </c>
       <c r="G5" t="n">
-        <v>108</v>
+        <v>1571</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>48.66</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19050</v>
+        <v>1275000</v>
       </c>
       <c r="K5" t="n">
-        <v>19450</v>
+        <v>1346000</v>
       </c>
       <c r="L5" t="n">
-        <v>22450</v>
+        <v>1381000</v>
       </c>
       <c r="M5" t="n">
-        <v>18430</v>
+        <v>1345000</v>
       </c>
       <c r="N5" t="n">
-        <v>0.18</v>
+        <v>48.69</v>
       </c>
       <c r="O5" t="n">
-        <v>56897163640</v>
+        <v>1947019453000</v>
       </c>
       <c r="P5" t="n">
-        <v>62100</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>14600</v>
+        <v>501000</v>
       </c>
       <c r="R5" t="n">
-        <v>7000</v>
+        <v>174000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>브릴스, 로봇 기업으로 빅웨이브 기대감. 기술 특례 상장 기업.</t>
+          <t>4조 규모 자사주 소각 및 주주환원 발표 기대감, 외국인/기관의 쌍끌이 매수를 근거로 15% 이상 상승 전망. 긍정적인 체결 강도 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇', '빅웨이브', '기술특례']</t>
+          <t>['자사주', '주주환원', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14940</v>
+        <v>223000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.06%</t>
+          <t>'+4.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>459</v>
       </c>
       <c r="G6" t="n">
-        <v>263</v>
+        <v>1988</v>
       </c>
       <c r="H6" t="n">
-        <v>10.02</v>
+        <v>46.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14220</v>
+        <v>213000</v>
       </c>
       <c r="K6" t="n">
-        <v>14390</v>
+        <v>222000</v>
       </c>
       <c r="L6" t="n">
-        <v>15150</v>
+        <v>225500</v>
       </c>
       <c r="M6" t="n">
-        <v>14390</v>
+        <v>221500</v>
       </c>
       <c r="N6" t="n">
-        <v>10.03</v>
+        <v>46.11</v>
       </c>
       <c r="O6" t="n">
-        <v>27020759065</v>
+        <v>1370191751250</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>392000</v>
+        <v>1019000</v>
       </c>
       <c r="S6" t="n">
-        <v>30000</v>
+        <v>432000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>영업이익 223% 증가라는 팩트 기반 실적 호조와 외국인/기관의 지속적인 매수세를 근거로 긍정적인 전망 제시. 공매도 물량 출회 예상.</t>
+          <t>정치적 이슈와 반도체 관련 뉴스가 혼재하며, 시장 참여자들 간의 의견이 분분함. SK하이닉스 ETF 퇴장 및 엔트로픽 HBM 부족 관련 뉴스가 언급됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['영업이익', '실적발표', '외국인', '기관']</t>
+          <t>['반도체', 'ETF', 'HBM']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>223250</v>
+        <v>14830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.81%</t>
+          <t>'+4.29%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
-        <v>459</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>2095</v>
+        <v>268</v>
       </c>
       <c r="H7" t="n">
-        <v>46.1</v>
+        <v>10.02</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>213000</v>
+        <v>14220</v>
       </c>
       <c r="K7" t="n">
-        <v>222000</v>
+        <v>14390</v>
       </c>
       <c r="L7" t="n">
-        <v>225500</v>
+        <v>15150</v>
       </c>
       <c r="M7" t="n">
-        <v>221500</v>
+        <v>14390</v>
       </c>
       <c r="N7" t="n">
-        <v>46.11</v>
+        <v>10.03</v>
       </c>
       <c r="O7" t="n">
-        <v>1316064245750</v>
+        <v>27878600380</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>1019000</v>
+        <v>392000</v>
       </c>
       <c r="S7" t="n">
-        <v>432000</v>
+        <v>30000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 삼성전자, 하이닉스 주가 상승에 대한 기대감이 언급되지만, 구체적인 근거는 부족함. 외인 비중 변화는 미미.</t>
+          <t>영업이익 223% 증가라는 팩트 기반 실적 호조와 외국인/기관의 지속적인 매수세를 근거로 긍정적인 전망 제시. 공매도 물량 출회 예상.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['선물주가', '주주환원', '주가조작']</t>
+          <t>['영업이익', '실적발표', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13980</v>
+        <v>62300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.48%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G8" t="n">
-        <v>191</v>
+        <v>658</v>
       </c>
       <c r="H8" t="n">
-        <v>2.82</v>
+        <v>40.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13380</v>
+        <v>59800</v>
       </c>
       <c r="K8" t="n">
-        <v>14000</v>
+        <v>60700</v>
       </c>
       <c r="L8" t="n">
-        <v>14410</v>
+        <v>63900</v>
       </c>
       <c r="M8" t="n">
-        <v>13710</v>
+        <v>60100</v>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>45989480125</v>
+        <v>171514614650</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>67300</v>
       </c>
       <c r="Q8" t="n">
-        <v>1760</v>
+        <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>-88000</v>
+        <v>195000</v>
       </c>
       <c r="S8" t="n">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대한광통신, 유리기판 특허 관련 기대감. 미국 전력 및 통신/반도체 업황 언급.</t>
+          <t>중동 관련 이슈 및 삼성그룹의 대규모 투자 계획 언급. 저평가 및 대형 수주 공시 기대감으로 인한 상승 전망이 있음. 공매도 움직임도 관찰됨.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유리기판', '특허', '업황']</t>
+          <t>['중동', '투자', '수주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,91 +1195,91 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62100</v>
+        <v>13880</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.85%</t>
+          <t>'+3.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>638</v>
+        <v>205</v>
       </c>
       <c r="H9" t="n">
-        <v>40.44</v>
+        <v>2.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>59800</v>
+        <v>13380</v>
       </c>
       <c r="K9" t="n">
-        <v>60700</v>
+        <v>14000</v>
       </c>
       <c r="L9" t="n">
-        <v>63900</v>
+        <v>14410</v>
       </c>
       <c r="M9" t="n">
-        <v>60100</v>
+        <v>13710</v>
       </c>
       <c r="N9" t="n">
-        <v>40.39</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>167511790000</v>
+        <v>47481811710</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>1760</v>
       </c>
       <c r="R9" t="n">
-        <v>195000</v>
+        <v>-88000</v>
       </c>
       <c r="S9" t="n">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성그룹 내 저평가 종목으로 언급되며, 중동 관련 사업 및 삼전/하닉 투자 연관성을 근거로 7만원 이상 상승 전망. 대형 수주 공시 기대.</t>
+          <t>대한광통신, 유리기판 특허 관련 기대감. 미국 전력 및 통신/반도체 업황 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['저평가', '대형수주', '공매도']</t>
+          <t>['유리기판', '특허', '업황']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16750</v>
+        <v>16630</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.76%</t>
+          <t>'+2.02%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
         <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="H10" t="n">
         <v>27.96</v>
@@ -1346,7 +1346,7 @@
         <v>27.94</v>
       </c>
       <c r="O10" t="n">
-        <v>24697438690</v>
+        <v>25984136200</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27000</v>
+        <v>26850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.89%</t>
+          <t>'+1.32%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H11" t="n">
         <v>12.32</v>
@@ -1438,7 +1438,7 @@
         <v>12.39</v>
       </c>
       <c r="O11" t="n">
-        <v>32665132375</v>
+        <v>34075811400</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,18 +1487,18 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14870</v>
+        <v>14820</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'+0.88%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.46</v>
       </c>
       <c r="E12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F12" t="n">
         <v>81</v>
@@ -1530,7 +1530,7 @@
         <v>7.36</v>
       </c>
       <c r="O12" t="n">
-        <v>61889746075</v>
+        <v>63207831500</v>
       </c>
       <c r="P12" t="n">
         <v>49800</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2040</v>
+        <v>2015</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.25%</t>
+          <t>'-0.98%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H13" t="n">
         <v>4.89</v>
@@ -1622,7 +1622,7 @@
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>15023442464</v>
+        <v>15665474056</v>
       </c>
       <c r="P13" t="n">
         <v>4980</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34700</v>
+        <v>34900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.93%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1708,13 +1708,13 @@
         <v>42150</v>
       </c>
       <c r="M14" t="n">
-        <v>34500</v>
+        <v>34250</v>
       </c>
       <c r="N14" t="n">
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>68692985425</v>
+        <v>76296977850</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>RF머트리얼즈, 영업이익 157% 상승에도 컨센서스 미달. 외국인/기관 순매수.</t>
+          <t>실적 발표 후 주가 변동성이 커졌으며, 컨센서스 미달에 대한 실망감이 나타남. 전년 대비 영업이익 상승에도 불구하고 주가는 하락세를 보임.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '컨센서스', '외국인']</t>
+          <t>['실적', '컨센서스', '영업이익']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">

--- a/data/trending_integrated_20261027_11.xlsx
+++ b/data/trending_integrated_20261027_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41590652030</v>
+        <v>41627250990</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18699108465</v>
+        <v>18701569425</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20600</v>
+        <v>20500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.14%</t>
+          <t>'+7.61%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -794,7 +794,7 @@
         <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>58313523265</v>
+        <v>59049898415</v>
       </c>
       <c r="P4" t="n">
         <v>62100</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1361000</v>
+        <v>1360000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.75%</t>
+          <t>'+6.67%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="G5" t="n">
-        <v>1571</v>
+        <v>1541</v>
       </c>
       <c r="H5" t="n">
         <v>48.66</v>
@@ -886,7 +886,7 @@
         <v>48.69</v>
       </c>
       <c r="O5" t="n">
-        <v>1947019453000</v>
+        <v>2004359843500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>4조 규모 자사주 소각 및 주주환원 발표 기대감, 외국인/기관의 쌍끌이 매수를 근거로 15% 이상 상승 전망. 긍정적인 체결 강도 확인.</t>
+          <t>SK하이닉스 자사주 4조 소각 예정, 앤트로픽 HBM 부족 언급. 외국인, 기관 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주', '주주환원', '외국인', '기관']</t>
+          <t>['자사주', 'HBM', '수급']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="G6" t="n">
-        <v>1988</v>
+        <v>1909</v>
       </c>
       <c r="H6" t="n">
         <v>46.1</v>
@@ -978,7 +978,7 @@
         <v>46.11</v>
       </c>
       <c r="O6" t="n">
-        <v>1370191751250</v>
+        <v>1422387879000</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈와 반도체 관련 뉴스가 혼재하며, 시장 참여자들 간의 의견이 분분함. SK하이닉스 ETF 퇴장 및 엔트로픽 HBM 부족 관련 뉴스가 언급됨.</t>
+          <t>삼성전자와 SK하이닉스에 대한 정치적 발언이 주를 이루며, HBM 부족과 RE100 관련 내용이 언급되었으나, 주가 관련 팩트 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', 'ETF', 'HBM']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14830</v>
+        <v>62300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.29%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>268</v>
+        <v>680</v>
       </c>
       <c r="H7" t="n">
-        <v>10.02</v>
+        <v>40.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14220</v>
+        <v>59800</v>
       </c>
       <c r="K7" t="n">
-        <v>14390</v>
+        <v>60700</v>
       </c>
       <c r="L7" t="n">
-        <v>15150</v>
+        <v>63900</v>
       </c>
       <c r="M7" t="n">
-        <v>14390</v>
+        <v>60100</v>
       </c>
       <c r="N7" t="n">
-        <v>10.03</v>
+        <v>40.39</v>
       </c>
       <c r="O7" t="n">
-        <v>27878600380</v>
+        <v>175016757000</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R7" t="n">
-        <v>392000</v>
+        <v>195000</v>
       </c>
       <c r="S7" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>영업이익 223% 증가라는 팩트 기반 실적 호조와 외국인/기관의 지속적인 매수세를 근거로 긍정적인 전망 제시. 공매도 물량 출회 예상.</t>
+          <t>중동 관련 이슈 및 삼성그룹의 대규모 투자 계획 언급. 저평가 및 대형 수주 공시 기대감으로 인한 상승 전망이 있음. 공매도 움직임도 관찰됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '실적발표', '외국인', '기관']</t>
+          <t>['중동', '투자', '수주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62300</v>
+        <v>14760</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+3.80%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>658</v>
+        <v>279</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>10.02</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59800</v>
+        <v>14220</v>
       </c>
       <c r="K8" t="n">
-        <v>60700</v>
+        <v>14390</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>15150</v>
       </c>
       <c r="M8" t="n">
-        <v>60100</v>
+        <v>14390</v>
       </c>
       <c r="N8" t="n">
-        <v>40.39</v>
+        <v>10.03</v>
       </c>
       <c r="O8" t="n">
-        <v>171514614650</v>
+        <v>28580949500</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>195000</v>
+        <v>392000</v>
       </c>
       <c r="S8" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>중동 관련 이슈 및 삼성그룹의 대규모 투자 계획 언급. 저평가 및 대형 수주 공시 기대감으로 인한 상승 전망이 있음. 공매도 움직임도 관찰됨.</t>
+          <t>대우건설 3분기 영업이익 223% 폭증 호실적 발표. 외국인, 기관 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['중동', '투자', '수주']</t>
+          <t>['영업이익', '실적', '호재']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13880</v>
+        <v>13840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.74%</t>
+          <t>'+3.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H9" t="n">
         <v>2.82</v>
@@ -1254,7 +1254,7 @@
         <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>47481811710</v>
+        <v>48586873855</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16630</v>
+        <v>16640</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.02%</t>
+          <t>'+2.09%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H10" t="n">
         <v>27.96</v>
@@ -1346,7 +1346,7 @@
         <v>27.94</v>
       </c>
       <c r="O10" t="n">
-        <v>25984136200</v>
+        <v>27047656995</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26850</v>
+        <v>26700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.32%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H11" t="n">
         <v>12.32</v>
@@ -1438,7 +1438,7 @@
         <v>12.39</v>
       </c>
       <c r="O11" t="n">
-        <v>34075811400</v>
+        <v>34568815450</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14820</v>
+        <v>14680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.88%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.46</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G12" t="n">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="H12" t="n">
         <v>7.82</v>
@@ -1530,7 +1530,7 @@
         <v>7.36</v>
       </c>
       <c r="O12" t="n">
-        <v>63207831500</v>
+        <v>65038860650</v>
       </c>
       <c r="P12" t="n">
         <v>49800</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2015</v>
+        <v>2000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.98%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="H13" t="n">
         <v>4.89</v>
@@ -1622,7 +1622,7 @@
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>15665474056</v>
+        <v>16163503865</v>
       </c>
       <c r="P13" t="n">
         <v>4980</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34900</v>
+        <v>34150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.38%</t>
+          <t>'-6.44%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1708,13 +1708,13 @@
         <v>42150</v>
       </c>
       <c r="M14" t="n">
-        <v>34250</v>
+        <v>33550</v>
       </c>
       <c r="N14" t="n">
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>76296977850</v>
+        <v>84008794075</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 변동성이 커졌으며, 컨센서스 미달에 대한 실망감이 나타남. 전년 대비 영업이익 상승에도 불구하고 주가는 하락세를 보임.</t>
+          <t>RF머트리얼즈 영업이익 157% 상승 발표했으나, 컨센서스 미달 및 주가 하락으로 인한 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '컨센서스', '영업이익']</t>
+          <t>['영업이익', '실적', '컨센서스']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261027_11.xlsx
+++ b/data/trending_integrated_20261027_11.xlsx
@@ -584,7 +584,7 @@
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41627250990</v>
+        <v>41661332980</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
         <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18701569425</v>
+        <v>18704713985</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 뉴스가 주가 급등의 주요 요인으로 작용. LG이노텍을 제치고 공급사로 채택되었다는 점이 부각되며 텐버거 기대감이 형성됨.</t>
+          <t>나무가, 휴머노이드 로봇 '아틀라스' 독점 공급 관련 기대감. 3D 센싱 카메라 기술 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['아틀라스', '휴머노이드', '공급망']</t>
+          <t>['아틀라스', '휴머노이드', '3D 센싱']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20500</v>
+        <v>20600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.61%</t>
+          <t>'+8.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -794,7 +794,7 @@
         <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>59049898415</v>
+        <v>59573415490</v>
       </c>
       <c r="P4" t="n">
         <v>62100</v>
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="G5" t="n">
-        <v>1541</v>
+        <v>1590</v>
       </c>
       <c r="H5" t="n">
         <v>48.66</v>
@@ -886,7 +886,7 @@
         <v>48.69</v>
       </c>
       <c r="O5" t="n">
-        <v>2004359843500</v>
+        <v>2046908458500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스 자사주 4조 소각 예정, 앤트로픽 HBM 부족 언급. 외국인, 기관 매수세 유입 확인.</t>
+          <t>SK하이닉스, 4조 자사주 소각 예정. 엔트로픽 관련 TCU 구매 약정 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주', 'HBM', '수급']</t>
+          <t>['자사주', 'TCU', '엔트로픽']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>223000</v>
+        <v>222750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.69%</t>
+          <t>'+4.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="G6" t="n">
-        <v>1909</v>
+        <v>1796</v>
       </c>
       <c r="H6" t="n">
         <v>46.1</v>
@@ -978,7 +978,7 @@
         <v>46.11</v>
       </c>
       <c r="O6" t="n">
-        <v>1422387879000</v>
+        <v>1464513508750</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자와 SK하이닉스에 대한 정치적 발언이 주를 이루며, HBM 부족과 RE100 관련 내용이 언급되었으나, 주가 관련 팩트 기반 분석은 부족함.</t>
+          <t>삼성전자, 30조 배당 및 자사주 매입 예고. HBM 부족은 위험 요인으로 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['배당', '자사주', 'HBM']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62300</v>
+        <v>14800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+4.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>680</v>
+        <v>293</v>
       </c>
       <c r="H7" t="n">
-        <v>40.44</v>
+        <v>10.02</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59800</v>
+        <v>14220</v>
       </c>
       <c r="K7" t="n">
-        <v>60700</v>
+        <v>14390</v>
       </c>
       <c r="L7" t="n">
-        <v>63900</v>
+        <v>15150</v>
       </c>
       <c r="M7" t="n">
-        <v>60100</v>
+        <v>14390</v>
       </c>
       <c r="N7" t="n">
-        <v>40.39</v>
+        <v>10.03</v>
       </c>
       <c r="O7" t="n">
-        <v>175016757000</v>
+        <v>29349174575</v>
       </c>
       <c r="P7" t="n">
-        <v>67300</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>23150</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>195000</v>
+        <v>392000</v>
       </c>
       <c r="S7" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>중동 관련 이슈 및 삼성그룹의 대규모 투자 계획 언급. 저평가 및 대형 수주 공시 기대감으로 인한 상승 전망이 있음. 공매도 움직임도 관찰됨.</t>
+          <t>대우건설, 3분기 영업이익 223% 증가. 외국인 및 기관 순매수 지속.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['중동', '투자', '수주']</t>
+          <t>['영업이익', '실적', '외국인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14760</v>
+        <v>62200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.80%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>279</v>
+        <v>699</v>
       </c>
       <c r="H8" t="n">
-        <v>10.02</v>
+        <v>40.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14220</v>
+        <v>59800</v>
       </c>
       <c r="K8" t="n">
-        <v>14390</v>
+        <v>60700</v>
       </c>
       <c r="L8" t="n">
-        <v>15150</v>
+        <v>63900</v>
       </c>
       <c r="M8" t="n">
-        <v>14390</v>
+        <v>60100</v>
       </c>
       <c r="N8" t="n">
-        <v>10.03</v>
+        <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>28580949500</v>
+        <v>176807147050</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>392000</v>
+        <v>195000</v>
       </c>
       <c r="S8" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대우건설 3분기 영업이익 223% 폭증 호실적 발표. 외국인, 기관 매수세 유입 확인.</t>
+          <t>삼성E&amp;A, 중동 관련 사업 기대감 및 저평가 인식. 대형 수주 공시 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['영업이익', '실적', '호재']</t>
+          <t>['중동', '수주', '저평가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13840</v>
+        <v>13830</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.44%</t>
+          <t>'+3.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="H9" t="n">
         <v>2.82</v>
@@ -1254,7 +1254,7 @@
         <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>48586873855</v>
+        <v>49045839045</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16640</v>
+        <v>16650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.09%</t>
+          <t>'+2.15%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H10" t="n">
         <v>27.96</v>
@@ -1346,7 +1346,7 @@
         <v>27.94</v>
       </c>
       <c r="O10" t="n">
-        <v>27047656995</v>
+        <v>27794595330</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26700</v>
+        <v>26900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.75%</t>
+          <t>'+1.51%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
         <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="H11" t="n">
         <v>12.32</v>
@@ -1438,7 +1438,7 @@
         <v>12.39</v>
       </c>
       <c r="O11" t="n">
-        <v>34568815450</v>
+        <v>35118868275</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14680</v>
+        <v>2035</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.46</v>
+        <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="F12" t="n">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>438</v>
+        <v>117</v>
       </c>
       <c r="H12" t="n">
-        <v>7.82</v>
+        <v>4.89</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14690</v>
+        <v>2035</v>
       </c>
       <c r="K12" t="n">
-        <v>14490</v>
+        <v>2035</v>
       </c>
       <c r="L12" t="n">
-        <v>15800</v>
+        <v>2145</v>
       </c>
       <c r="M12" t="n">
-        <v>14260</v>
+        <v>1953</v>
       </c>
       <c r="N12" t="n">
-        <v>7.36</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>65038860650</v>
+        <v>16494486338</v>
       </c>
       <c r="P12" t="n">
-        <v>49800</v>
+        <v>4980</v>
       </c>
       <c r="Q12" t="n">
-        <v>8180</v>
+        <v>749</v>
       </c>
       <c r="R12" t="n">
-        <v>264000</v>
+        <v>-89000</v>
       </c>
       <c r="S12" t="n">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>해외 수출 및 신약 개발 활용을 근거로 AI 신약 개발 분야의 성장성과 확장성을 강조. 공매도 숏커버링 발생 가능성 및 서밋테라퓨틱스 협력 주목.</t>
+          <t>앤로보틱스, 주가 변동성에 대한 언급. 로보월드 행사 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 신약', '수출', '공매도', '숏커버링']</t>
+          <t>['로보월드', '변동성', '개미털기']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2000</v>
+        <v>14630</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.11</v>
+        <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>119</v>
+        <v>443</v>
       </c>
       <c r="H13" t="n">
-        <v>4.89</v>
+        <v>7.82</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2035</v>
+        <v>14690</v>
       </c>
       <c r="K13" t="n">
-        <v>2035</v>
+        <v>14490</v>
       </c>
       <c r="L13" t="n">
-        <v>2145</v>
+        <v>15800</v>
       </c>
       <c r="M13" t="n">
-        <v>1953</v>
+        <v>14260</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>16163503865</v>
+        <v>65823454590</v>
       </c>
       <c r="P13" t="n">
-        <v>4980</v>
+        <v>49800</v>
       </c>
       <c r="Q13" t="n">
-        <v>749</v>
+        <v>8180</v>
       </c>
       <c r="R13" t="n">
-        <v>-89000</v>
+        <v>264000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>앤로보틱스, 주가 변동성에 대한 언급. 로보월드 행사 기대감.</t>
+          <t>해외 수출 및 신약 개발 활용을 근거로 AI 신약 개발 분야의 성장성과 확장성을 강조. 공매도 숏커버링 발생 가능성 및 서밋테라퓨틱스 협력 주목.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로보월드', '변동성', '개미털기']</t>
+          <t>['AI 신약', '수출', '공매도', '숏커버링']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34150</v>
+        <v>34600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.44%</t>
+          <t>'-5.21%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>84008794075</v>
+        <v>86453682775</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>RF머트리얼즈 영업이익 157% 상승 발표했으나, 컨센서스 미달 및 주가 하락으로 인한 부정적 전망.</t>
+          <t>RF머트리얼즈, 영업이익 157% 상승했으나 시장 기대치 미달. 단기 변동성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '실적', '컨센서스']</t>
+          <t>['영업이익', '컨센서스', '실적']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261027_11.xlsx
+++ b/data/trending_integrated_20261027_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41661332980</v>
+        <v>41719492400</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18704713985</v>
+        <v>18706303355</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>나무가, 휴머노이드 로봇 '아틀라스' 독점 공급 관련 기대감. 3D 센싱 카메라 기술 부각.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 나무가 단독 공급 소식. LG이노텍 제치고 채택, 3D센싱 카메라 독점 공급으로 텐버거 기대감 고조. 3분기 실적 어닝 서프라이즈 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['아틀라스', '휴머노이드', '3D 센싱']</t>
+          <t>['휴머노이드', '아틀라스', '3D센싱']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20600</v>
+        <v>20250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.14%</t>
+          <t>'+6.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
         <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -794,7 +794,7 @@
         <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>59573415490</v>
+        <v>59965939790</v>
       </c>
       <c r="P4" t="n">
         <v>62100</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1360000</v>
+        <v>1349000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.67%</t>
+          <t>'+5.80%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G5" t="n">
-        <v>1590</v>
+        <v>1551</v>
       </c>
       <c r="H5" t="n">
         <v>48.66</v>
@@ -886,7 +886,7 @@
         <v>48.69</v>
       </c>
       <c r="O5" t="n">
-        <v>2046908458500</v>
+        <v>2146900535000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스, 4조 자사주 소각 예정. 엔트로픽 관련 TCU 구매 약정 언급.</t>
+          <t>실적 발표 이후 매수 권유 및 5% 이상 상승 예측. 외국인, 기관 쌍끌이 매수세와 높은 체결 강도 확인, 주주환원 발표 기대감 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주', 'TCU', '엔트로픽']</t>
+          <t>['실적', '외국인', '체결강도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>222750</v>
+        <v>222000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="G6" t="n">
-        <v>1796</v>
+        <v>1600</v>
       </c>
       <c r="H6" t="n">
         <v>46.1</v>
@@ -972,13 +972,13 @@
         <v>225500</v>
       </c>
       <c r="M6" t="n">
-        <v>221500</v>
+        <v>221000</v>
       </c>
       <c r="N6" t="n">
         <v>46.11</v>
       </c>
       <c r="O6" t="n">
-        <v>1464513508750</v>
+        <v>1541856226000</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자, 30조 배당 및 자사주 매입 예고. HBM 부족은 위험 요인으로 언급.</t>
+          <t>국내외 선물 급등과 함께 삼성전자 7% 상승 전망 언급. 그러나 외인 매도 시작, SK하이닉스 ETF 퇴장 및 HBM 부족 우려 뉴스가 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['배당', '자사주', 'HBM']</t>
+          <t>['선물', 'HBM', '외인']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14800</v>
+        <v>14790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.08%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="H7" t="n">
         <v>10.02</v>
@@ -1070,7 +1070,7 @@
         <v>10.03</v>
       </c>
       <c r="O7" t="n">
-        <v>29349174575</v>
+        <v>30189616450</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62200</v>
+        <v>62100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+3.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="H8" t="n">
         <v>40.44</v>
@@ -1162,7 +1162,7 @@
         <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>176807147050</v>
+        <v>180463811000</v>
       </c>
       <c r="P8" t="n">
         <v>67300</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13830</v>
+        <v>13750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.36%</t>
+          <t>'+2.77%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="H9" t="n">
         <v>2.82</v>
@@ -1254,7 +1254,7 @@
         <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>49045839045</v>
+        <v>50622403830</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16650</v>
+        <v>16600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.15%</t>
+          <t>'+1.84%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
         <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H10" t="n">
         <v>27.96</v>
@@ -1346,7 +1346,7 @@
         <v>27.94</v>
       </c>
       <c r="O10" t="n">
-        <v>27794595330</v>
+        <v>28571435945</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26900</v>
+        <v>26750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.51%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H11" t="n">
         <v>12.32</v>
@@ -1438,7 +1438,7 @@
         <v>12.39</v>
       </c>
       <c r="O11" t="n">
-        <v>35118868275</v>
+        <v>35558015675</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2035</v>
+        <v>2050</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
         <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H12" t="n">
         <v>4.89</v>
@@ -1530,7 +1530,7 @@
         <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>16494486338</v>
+        <v>16908004838</v>
       </c>
       <c r="P12" t="n">
         <v>4980</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14630</v>
+        <v>14500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.41%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" t="n">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>65823454590</v>
+        <v>67223266020</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>해외 수출 및 신약 개발 활용을 근거로 AI 신약 개발 분야의 성장성과 확장성을 강조. 공매도 숏커버링 발생 가능성 및 서밋테라퓨틱스 협력 주목.</t>
+          <t>거래금액 폭등 및 프로그램/외인/기관 매수 우위 지속. Lunit스코프 AI 신약 개발 활용 및 서밋테라퓨틱스 선택 등 성장성 확장성 확고.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI 신약', '수출', '공매도', '숏커버링']</t>
+          <t>['AI', '신약개발', '성장성']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34600</v>
+        <v>34450</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.21%</t>
+          <t>'-5.62%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G14" t="n">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>86453682775</v>
+        <v>87940100575</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>RF머트리얼즈, 영업이익 157% 상승했으나 시장 기대치 미달. 단기 변동성.</t>
+          <t>실적 양호(영업이익 전년비 157% 상승)에도 불구하고 주가 하락세. 외인 매도세 관찰되며, 루멘텀 급등 및 엔트로픽 관련 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '컨센서스', '실적']</t>
+          <t>['실적', '외인', '루멘텀']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261027_11.xlsx
+++ b/data/trending_integrated_20261027_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41719492400</v>
+        <v>41759621450</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18706303355</v>
+        <v>18708268705</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 나무가 단독 공급 소식. LG이노텍 제치고 채택, 3D센싱 카메라 독점 공급으로 텐버거 기대감 고조. 3분기 실적 어닝 서프라이즈 가능성 언급.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 나무가의 독점 공급 관련 호재 부각. 3분기 어닝 서프라이즈 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['휴머노이드', '아틀라스', '3D센싱']</t>
+          <t>['아틀라스', '휴머노이드', '로봇']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20250</v>
+        <v>20550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.30%</t>
+          <t>'+7.87%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -794,7 +794,7 @@
         <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>59965939790</v>
+        <v>60391695740</v>
       </c>
       <c r="P4" t="n">
         <v>62100</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1349000</v>
+        <v>1348000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.80%</t>
+          <t>'+5.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="G5" t="n">
-        <v>1551</v>
+        <v>1473</v>
       </c>
       <c r="H5" t="n">
         <v>48.66</v>
@@ -880,13 +880,13 @@
         <v>1381000</v>
       </c>
       <c r="M5" t="n">
-        <v>1345000</v>
+        <v>1344000</v>
       </c>
       <c r="N5" t="n">
         <v>48.69</v>
       </c>
       <c r="O5" t="n">
-        <v>2146900535000</v>
+        <v>2201748361000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>실적 발표 이후 매수 권유 및 5% 이상 상승 예측. 외국인, 기관 쌍끌이 매수세와 높은 체결 강도 확인, 주주환원 발표 기대감 존재.</t>
+          <t>실적 발표 이후 매수 전략 및 외국인, 기관 동반 매수세 관찰. 주주환원 발표 기대감 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적', '외국인', '체결강도']</t>
+          <t>['실적발표', '외국인기관', '주주환원']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,123 +931,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>222000</v>
+        <v>2130</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.23%</t>
+          <t>'+4.67%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>447</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>1600</v>
+        <v>119</v>
       </c>
       <c r="H6" t="n">
-        <v>46.1</v>
+        <v>4.89</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>213000</v>
+        <v>2035</v>
       </c>
       <c r="K6" t="n">
-        <v>222000</v>
+        <v>2035</v>
       </c>
       <c r="L6" t="n">
-        <v>225500</v>
+        <v>2145</v>
       </c>
       <c r="M6" t="n">
-        <v>221000</v>
+        <v>1953</v>
       </c>
       <c r="N6" t="n">
-        <v>46.11</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>1541856226000</v>
+        <v>19669641641</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>4980</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>749</v>
       </c>
       <c r="R6" t="n">
-        <v>1019000</v>
+        <v>-89000</v>
       </c>
       <c r="S6" t="n">
-        <v>432000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>국내외 선물 급등과 함께 삼성전자 7% 상승 전망 언급. 그러나 외인 매도 시작, SK하이닉스 ETF 퇴장 및 HBM 부족 우려 뉴스가 혼재.</t>
+          <t>앤로보틱스, 주가 변동성에 대한 언급. 로보월드 행사 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['선물', 'HBM', '외인']</t>
+          <t>['로보월드', '변동성', '개미털기']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14790</v>
+        <v>62400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+4.35%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>299</v>
+        <v>728</v>
       </c>
       <c r="H7" t="n">
-        <v>10.02</v>
+        <v>40.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14220</v>
+        <v>59800</v>
       </c>
       <c r="K7" t="n">
-        <v>14390</v>
+        <v>60700</v>
       </c>
       <c r="L7" t="n">
-        <v>15150</v>
+        <v>63900</v>
       </c>
       <c r="M7" t="n">
-        <v>14390</v>
+        <v>60100</v>
       </c>
       <c r="N7" t="n">
-        <v>10.03</v>
+        <v>40.39</v>
       </c>
       <c r="O7" t="n">
-        <v>30189616450</v>
+        <v>183311750550</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R7" t="n">
-        <v>392000</v>
+        <v>195000</v>
       </c>
       <c r="S7" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대우건설, 3분기 영업이익 223% 증가. 외국인 및 기관 순매수 지속.</t>
+          <t>삼성E&amp;A, 중동 관련 사업 기대감 및 저평가 인식. 대형 수주 공시 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '실적', '외국인']</t>
+          <t>['중동', '수주', '저평가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62100</v>
+        <v>222000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.85%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>116</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>453</v>
       </c>
       <c r="G8" t="n">
-        <v>710</v>
+        <v>1387</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K8" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>225500</v>
       </c>
       <c r="M8" t="n">
-        <v>60100</v>
+        <v>221000</v>
       </c>
       <c r="N8" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>180463811000</v>
+        <v>1595173905500</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>195000</v>
+        <v>1019000</v>
       </c>
       <c r="S8" t="n">
-        <v>15000</v>
+        <v>432000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 중동 관련 사업 기대감 및 저평가 인식. 대형 수주 공시 가능성 언급.</t>
+          <t>SK하이닉스 ETF의 미국 증시 퇴장 및 HBM 부족 위험 요인 언급. 일부 긍정적인 전망 속 외인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['중동', '수주', '저평가']</t>
+          <t>['HBM', '외인매도', 'ETF']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,169 +1200,169 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13750</v>
+        <v>14800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.77%</t>
+          <t>'+4.08%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="H9" t="n">
-        <v>2.82</v>
+        <v>10.02</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13380</v>
+        <v>14220</v>
       </c>
       <c r="K9" t="n">
-        <v>14000</v>
+        <v>14390</v>
       </c>
       <c r="L9" t="n">
-        <v>14410</v>
+        <v>15150</v>
       </c>
       <c r="M9" t="n">
-        <v>13710</v>
+        <v>14390</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>10.03</v>
       </c>
       <c r="O9" t="n">
-        <v>50622403830</v>
+        <v>30693510820</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>1760</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-88000</v>
+        <v>392000</v>
       </c>
       <c r="S9" t="n">
-        <v>6000</v>
+        <v>30000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대한광통신, 유리기판 특허 관련 기대감. 미국 전력 및 통신/반도체 업황 언급.</t>
+          <t>3분기 영업이익 223% 증가 확인. 외국인, 기관 프로그램 매수세 지속 관찰.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유리기판', '특허', '업황']</t>
+          <t>['영업이익', '실적발표', '외국인기관']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16600</v>
+        <v>13850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.84%</t>
+          <t>'+3.51%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="H10" t="n">
-        <v>27.96</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16300</v>
+        <v>13380</v>
       </c>
       <c r="K10" t="n">
-        <v>16410</v>
+        <v>14000</v>
       </c>
       <c r="L10" t="n">
-        <v>16770</v>
+        <v>14410</v>
       </c>
       <c r="M10" t="n">
-        <v>16410</v>
+        <v>13710</v>
       </c>
       <c r="N10" t="n">
-        <v>27.94</v>
+        <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>28571435945</v>
+        <v>51275925990</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>16290</v>
+        <v>1760</v>
       </c>
       <c r="R10" t="n">
-        <v>118000</v>
+        <v>-88000</v>
       </c>
       <c r="S10" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성중공업, 주가 조작 및 공매도 관련 불만 표출. 조선주 하락세 언급.</t>
+          <t>대한광통신, 유리기판 특허 관련 기대감. 미국 전력 및 통신/반도체 업황 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '조선주']</t>
+          <t>['유리기판', '특허', '업황']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26750</v>
+        <v>16610</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+1.90%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H11" t="n">
-        <v>12.32</v>
+        <v>27.96</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>26500</v>
+        <v>16300</v>
       </c>
       <c r="K11" t="n">
-        <v>26600</v>
+        <v>16410</v>
       </c>
       <c r="L11" t="n">
-        <v>27200</v>
+        <v>16770</v>
       </c>
       <c r="M11" t="n">
-        <v>25350</v>
+        <v>16410</v>
       </c>
       <c r="N11" t="n">
-        <v>12.39</v>
+        <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>35558015675</v>
+        <v>29208042495</v>
       </c>
       <c r="P11" t="n">
-        <v>59300</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>22000</v>
+        <v>16290</v>
       </c>
       <c r="R11" t="n">
-        <v>-225000</v>
+        <v>118000</v>
       </c>
       <c r="S11" t="n">
-        <v>-32000</v>
+        <v>1000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 실적 예상치 하향 및 부정적 전망. 개인 매수세만 관찰됨.</t>
+          <t>삼성중공업, 주가 조작 및 공매도 관련 불만 표출. 조선주 하락세 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', 'AMPC', '개인매수']</t>
+          <t>['주가조작', '공매도', '조선주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2050</v>
+        <v>26850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.74%</t>
+          <t>'+1.32%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="H12" t="n">
-        <v>4.89</v>
+        <v>12.32</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2035</v>
+        <v>26500</v>
       </c>
       <c r="K12" t="n">
-        <v>2035</v>
+        <v>26600</v>
       </c>
       <c r="L12" t="n">
-        <v>2145</v>
+        <v>27200</v>
       </c>
       <c r="M12" t="n">
-        <v>1953</v>
+        <v>25350</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>12.39</v>
       </c>
       <c r="O12" t="n">
-        <v>16908004838</v>
+        <v>36243141075</v>
       </c>
       <c r="P12" t="n">
-        <v>4980</v>
+        <v>59300</v>
       </c>
       <c r="Q12" t="n">
-        <v>749</v>
+        <v>22000</v>
       </c>
       <c r="R12" t="n">
-        <v>-89000</v>
+        <v>-225000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-32000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>앤로보틱스, 주가 변동성에 대한 언급. 로보월드 행사 기대감.</t>
+          <t>3분기 실적 예상치 하향 및 부정적 전망. 개인 매수세만 관찰됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['로보월드', '변동성', '개미털기']</t>
+          <t>['실적', 'AMPC', '개인매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14500</v>
+        <v>14420</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-1.84%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F13" t="n">
         <v>85</v>
       </c>
       <c r="G13" t="n">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>67223266020</v>
+        <v>68399188355</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34450</v>
+        <v>34400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.62%</t>
+          <t>'-5.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H14" t="n">
         <v>8.65</v>
@@ -1714,7 +1714,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>87940100575</v>
+        <v>89674546150</v>
       </c>
       <c r="P14" t="n">
         <v>126600</v>
